--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.4.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.4.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1035,7 +1035,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.4.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00219_18600707/oocihm.N_00219_18600707.4.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y137"/>
+  <dimension ref="A1:Y145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -617,16 +617,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L14: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: For all four of the Reviews, .â€¦, .â€¦</t>
+          <t>L63: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: Yearly, 85; Half-yearly. 2.50 ； Quarter-</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: Â¥-</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L8: symbol-only separator/garbage line :: $3 00</t>
@@ -634,7 +638,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L1: isolated marker/symbol line :: ï»¿</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | isolated marker/symbol line :: [BOM]</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr">
@@ -644,7 +648,7 @@
       </c>
       <c r="Q2" s="1" t="inlineStr">
         <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: quote/punctuation debris :: unto the third and fourth generation ; indeed, â€”., 171.</t>
+          <t>L136: punctuation artifact: repeated periods :: For any one of the four Reviews ...</t>
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr">
@@ -689,7 +693,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1366</t>
+          <t>924</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -716,12 +720,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L51: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: pamphlet of â€œPriced Specimens of Fonts."</t>
+          <t>L78: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: Bound Volumes ， containing 1 mbers, at</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œthe cosmetics and other toilet</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: ¥-</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -733,7 +737,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: Â¥-</t>
+          <t>L5: stray/suspicious non-ASCII glyph(s): U+00A5 YEN SIGN | isolated marker/symbol line :: ¥-</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -743,7 +747,7 @@
       </c>
       <c r="Q3" s="1" t="inlineStr">
         <is>
-          <t>L136: punctuation artifact: repeated periods :: For any one of the four Reviews ...</t>
+          <t>L142: punctuation artifact: double/multiple hyphen :: For Blackwood’s Magazine, -------</t>
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr">
@@ -815,12 +819,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA :: ä¸Š</t>
+          <t>L148: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: OUR MUSICAL FRIEND. Scrofula, or Kingâ€™s Evil,</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): s5 (letter/digit mix) :: 9 00 Yearly, s5; Half yearly 89.50 • Quarter-</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -842,13 +846,13 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: For Blackwoodâ€™s Magazine, -------</t>
+          <t>L185: punctuation artifact: repeated periods :: LEONARD SCOTT &amp; Co.. $2.50 each constantly on hand</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
       <c r="S4" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________â€” ------------- ----: ---107 Nassau St., New York.</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •Subscribe to . Our Musical Friend," or</t>
         </is>
       </c>
       <c r="T4" s="1" t="inlineStr"/>
@@ -870,12 +874,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>249</t>
+          <t>252</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>171</t>
+          <t>125</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -902,12 +906,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L218: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L170: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”is a constitutional disease, a corruption of the</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •Subscribe to . Our Musical Friend," or</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -929,19 +933,19 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L185: punctuation artifact: repeated periods :: LEONARD SCOTT &amp; Co.. $2.50 each constantly on hand</t>
+          <t>L191: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________— ------------- ----: ---107 Nassau St., New York.</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
       <c r="S5" s="1" t="inlineStr">
         <is>
-          <t>L234: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --cessful practice in Europe and America</t>
+          <t>L191: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________— ------------- ----: ---107 Nassau St., New York.</t>
         </is>
       </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr">
         <is>
-          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with Â© Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
+          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with © Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
         </is>
       </c>
       <c r="V5" s="1" t="inlineStr"/>
@@ -980,17 +984,17 @@
       </c>
       <c r="I6" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): s5 (letter/digit mix) :: 9 00 Yearly, s5; Half yearly 89.50 â€¢ Quarter-</t>
+          <t>L77: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | suspicious token(s): s5 (letter/digit mix) :: 9 00 Yearly, s5; Half yearly 89.50 • Quarter-</t>
         </is>
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L329: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L187: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L77: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | suspicious token(s): s5 (letter/digit mix) :: 9 00 Yearly, s5; Half yearly 89.50 â€¢ Quarter-</t>
+          <t>L111: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: it seems to be the rod of Him who says, •• I Both the Ointment and Pills should be</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -1012,13 +1016,13 @@
       </c>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________â€” ------------- ----: ---107 Nassau St., New York.</t>
+          <t>L230: punctuation artifact: double/multiple hyphen :: _— ______________- ----------------— The treatment they adopt is the result of</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
       <c r="S6" s="1" t="inlineStr">
         <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: _________________________â€” â€” correct detail of their cases witha remit-</t>
+          <t>L234: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --cessful practice in Europe and America</t>
         </is>
       </c>
       <c r="T6" s="1" t="inlineStr"/>
@@ -1068,12 +1072,12 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L206: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢Subscribe to . Our Musical Friend," or</t>
+          <t>L285: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •information to be had on applying at the complaints, or from whom genuine European , ALICE Tell</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -1095,13 +1099,13 @@
       </c>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: _â€” ______________- ----------------â€” The treatment they adopt is the result of</t>
+          <t>L234: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --cessful practice in Europe and America</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
       <c r="S7" s="1" t="inlineStr">
         <is>
-          <t>L311: line starts with punctuation glued to text :: .the experience of one nation, but consists of</t>
+          <t>L285: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: •information to be had on applying at the complaints, or from whom genuine European , ALICE Tell</t>
         </is>
       </c>
       <c r="T7" s="1" t="inlineStr"/>
@@ -1147,12 +1151,12 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L346: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L218: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L109: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: quote/punctuation debris :: unto the third and fourth generation ; indeed, â€”., 171.</t>
+          <t>L289: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: 1. C HART, Persons IN ANY PART OF THE WORLD • of -----</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1164,7 +1168,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L390: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L390: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr">
@@ -1174,13 +1178,13 @@
       </c>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L234: punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: --cessful practice in Europe and America</t>
+          <t>L246: punctuation artifact: repeated periods :: VALLA..............DR. AMOS &amp; SON takes pleasure in rilla is to purify and regenerate thisvitalfluid,</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
       <c r="S8" s="1" t="inlineStr">
         <is>
-          <t>L474: line starts with punctuation glued to text :: ** Sold at the Manufactory of Professor</t>
+          <t>L292: line starts with punctuation glued to text :: _________________________— — correct detail of their cases witha remit-</t>
         </is>
       </c>
       <c r="T8" s="1" t="inlineStr"/>
@@ -1226,12 +1230,12 @@
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L382: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN :: SÉ™liitor</t>
+          <t>L299: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心 '</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L111: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: it seems to be the rod of Him who says, â€¢â€¢ I Both the Ointment and Pills should be</t>
+          <t>L390: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1249,13 +1253,13 @@
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>L246: punctuation artifact: repeated periods :: VALLA..............DR. AMOS &amp; SON takes pleasure in rilla is to purify and regenerate thisvitalfluid,</t>
+          <t>L268: punctuation artifact: repeated periods :: Head Office....Church Street, Toronto: Persons wishing the above usefulinstru-</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr"/>
       <c r="S9" s="1" t="inlineStr">
         <is>
-          <t>L551: line starts with punctuation glued to text :: .ROBE</t>
+          <t>L311: line starts with punctuation glued to text :: .the experience of one nation, but consists of</t>
         </is>
       </c>
       <c r="T9" s="1" t="inlineStr"/>
@@ -1278,7 +1282,7 @@
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>24</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1301,12 +1305,12 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L387: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A6 BROKEN BAR :: Head Ofice â€¦. Church Street. Toronto:</t>
+          <t>L329: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L142: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | punctuation artifact: double/multiple hyphen :: For Blackwoodâ€™s Magazine, -------</t>
+          <t>L398: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • YS</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1324,13 +1328,13 @@
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>L268: punctuation artifact: repeated periods :: Head Office....Church Street, Toronto: Persons wishing the above usefulinstru-</t>
+          <t>L289: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: double/multiple hyphen :: 1. C HART, Persons IN ANY PART OF THE WORLD • of -----</t>
         </is>
       </c>
       <c r="R10" s="1" t="inlineStr"/>
       <c r="S10" s="1" t="inlineStr">
         <is>
-          <t>L591: line starts with punctuation glued to text :: .Dysentery. Dropsy</t>
+          <t>L398: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • YS</t>
         </is>
       </c>
       <c r="T10" s="1" t="inlineStr"/>
@@ -1353,7 +1357,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1376,12 +1380,12 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L452: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): m0s (letter/digit mix) :: m0sâ€ skeptical as to the merits of their in-</t>
+          <t>L333: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen | line starts with punctuation glued to text :: ____________â€” ------------- ----: ---107 Nassau St., New York.</t>
+          <t>L443: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: known in the world for the•</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
@@ -1399,13 +1403,13 @@
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: 1. C HART, Persons IN ANY PART OF THE WORLD â€¢ of -----</t>
+          <t>L329: punctuation artifact: repeated periods :: From the time I first discovered its dropp ng..</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
       <c r="S11" s="1" t="inlineStr">
         <is>
-          <t>L599: line starts with digit/letter garbage token | suspicious token(s): 1Morbus (letter/digit mix) :: 1Morbus, I give it to you at the request of Mr Bradford</t>
+          <t>L474: line starts with punctuation glued to text :: ** Sold at the Manufactory of Professor</t>
         </is>
       </c>
       <c r="T11" s="1" t="inlineStr"/>
@@ -1423,7 +1427,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>144</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1451,12 +1455,12 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L523: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‹</t>
+          <t>L343: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L202: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: or cash, at Bruceâ€™s New York Type Foundry.</t>
+          <t>L506: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Hair Restorative’ which he liked very much</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
@@ -1474,13 +1478,13 @@
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>L329: punctuation artifact: repeated periods :: From the time I first discovered its dropp ng..</t>
+          <t>L367: punctuation artifact: double/multiple hyphen :: Such a medicine we supply in - -----——</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr"/>
       <c r="S12" s="1" t="inlineStr">
         <is>
-          <t>L644: line starts with punctuation glued to text :: .tifiestesin my pos</t>
+          <t>L506: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Hair Restorative’ which he liked very much</t>
         </is>
       </c>
       <c r="T12" s="1" t="inlineStr"/>
@@ -1526,12 +1530,12 @@
       </c>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L651: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L346: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L220: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: taining it. will be allowed his bill, at the time â€” New York,</t>
+          <t>L601: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: €holers Infantum You can sell a great deal of your Hair Resto-</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
@@ -1543,19 +1547,19 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L791: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L791: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
       <c r="Q13" s="1" t="inlineStr">
         <is>
-          <t>L367: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Such a medicine we supply in - -----â€”â€”</t>
+          <t>L517: punctuation artifact: repeated periods :: ing the larger sizes..</t>
         </is>
       </c>
       <c r="R13" s="1" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr">
         <is>
-          <t>L842: line starts with punctuation glued to text :: .w high all express in ly. if neglected, end which have now stood the test of public exp-</t>
+          <t>L551: line starts with punctuation glued to text :: .ROBE</t>
         </is>
       </c>
       <c r="T13" s="1" t="inlineStr"/>
@@ -1578,7 +1582,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1601,12 +1605,12 @@
       </c>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L653: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): A1001 (letter/digit mix) :: â€” A1001</t>
+          <t>L482: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L226: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: GEORGE BRUCE. 8 oâ€™clock in the morning, until 9 at night in</t>
+          <t>L649: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: dividual taking it•</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
@@ -1624,13 +1628,13 @@
       <c r="P14" s="1" t="inlineStr"/>
       <c r="Q14" s="1" t="inlineStr">
         <is>
-          <t>L517: punctuation artifact: repeated periods :: ing the larger sizes..</t>
+          <t>L671: punctuation artifact: repeated periods :: [Medicine .. It will press the obligations I am under for the entire</t>
         </is>
       </c>
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="1" t="inlineStr">
         <is>
-          <t>L1124: line starts with digit/letter garbage token | suspicious token(s): 1Wholesale (letter/digit mix) :: 1Wholesale and for Exportation by the</t>
+          <t>L591: line starts with punctuation glued to text :: .Dysentery. Dropsy</t>
         </is>
       </c>
       <c r="T14" s="1" t="inlineStr"/>
@@ -1666,7 +1670,7 @@
       <c r="G15" s="1" t="inlineStr"/>
       <c r="H15" s="1" t="inlineStr">
         <is>
-          <t>L452: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): m0s (letter/digit mix) :: m0sâ€ skeptical as to the merits of their in-</t>
+          <t>L452: suspicious token(s): m0s (letter/digit mix) :: m0s† skeptical as to the merits of their in-</t>
         </is>
       </c>
       <c r="I15" s="1" t="inlineStr">
@@ -1676,12 +1680,12 @@
       </c>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L657: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L564: stray/suspicious non-ASCII glyph(s): U+56DB CJK UNIFIED IDEOGRAPH-56DB | isolated marker/symbol line :: 四</t>
         </is>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L230: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: _â€” ______________- ----------------â€” The treatment they adopt is the result of</t>
+          <t>L652: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gently on the Bowel- ©</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
@@ -1693,17 +1697,21 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L854: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L854: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
       <c r="Q15" s="1" t="inlineStr">
         <is>
-          <t>L671: punctuation artifact: repeated periods :: [Medicine .. It will press the obligations I am under for the entire</t>
+          <t>L719: punctuation artifact: repeated periods :: Solicitor.........- Angus Morrison, Esq.</t>
         </is>
       </c>
       <c r="R15" s="1" t="inlineStr"/>
-      <c r="S15" s="1" t="inlineStr"/>
+      <c r="S15" s="1" t="inlineStr">
+        <is>
+          <t>L599: line starts with digit/letter garbage token | suspicious token(s): 1Morbus (letter/digit mix) :: 1Morbus, I give it to you at the request of Mr Bradford</t>
+        </is>
+      </c>
       <c r="T15" s="1" t="inlineStr"/>
       <c r="U15" s="1" t="inlineStr"/>
       <c r="V15" s="1" t="inlineStr"/>
@@ -1747,19 +1755,19 @@
       </c>
       <c r="J16" s="1" t="inlineStr">
         <is>
-          <t>L726: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: pr Ã© es thr obligations I om under for tbe entir</t>
+          <t>L651: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L232: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: CAN ADA upwards of 30 yearsâ€™ extensive and and sue</t>
+          <t>L673: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN :: ™ thousands can about the time of my arrival in the United</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L150: isolated marker/symbol line :: A</t>
+          <t>L148: stray/suspicious non-ASCII glyph(s): U+4E0A CJK UNIFIED IDEOGRAPH-4E0A | isolated marker/symbol line :: 上</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1770,11 +1778,15 @@
       <c r="P16" s="1" t="inlineStr"/>
       <c r="Q16" s="1" t="inlineStr">
         <is>
-          <t>L719: punctuation artifact: repeated periods :: Solicitor.........- Angus Morrison, Esq.</t>
+          <t>L721: punctuation artifact: repeated periods :: Bankers.............BANK UP. CANADA</t>
         </is>
       </c>
       <c r="R16" s="1" t="inlineStr"/>
-      <c r="S16" s="1" t="inlineStr"/>
+      <c r="S16" s="1" t="inlineStr">
+        <is>
+          <t>L644: line starts with punctuation glued to text :: .tifiestesin my pos</t>
+        </is>
+      </c>
       <c r="T16" s="1" t="inlineStr"/>
       <c r="U16" s="1" t="inlineStr"/>
       <c r="V16" s="1" t="inlineStr"/>
@@ -1818,19 +1830,19 @@
       </c>
       <c r="J17" s="1" t="inlineStr">
         <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): grDB (odd internal casing) :: CAUTIONâ€” X e grDB nless</t>
+          <t>L657: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L276: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: tedâ€” inst loss or damage - A CURE WARRANTED- for their use in the following co maiserder</t>
+          <t>L700: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: • • Sold at the Manufactories of Professor</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L151: isolated marker/symbol line :: 8</t>
+          <t>L150: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1841,11 +1853,15 @@
       <c r="P17" s="1" t="inlineStr"/>
       <c r="Q17" s="1" t="inlineStr">
         <is>
-          <t>L721: punctuation artifact: repeated periods :: Bankers.............BANK UP. CANADA</t>
+          <t>L734: punctuation artifact: double/multiple hyphen :: e ------------------------ - - cures and directions</t>
         </is>
       </c>
       <c r="R17" s="1" t="inlineStr"/>
-      <c r="S17" s="1" t="inlineStr"/>
+      <c r="S17" s="1" t="inlineStr">
+        <is>
+          <t>L842: line starts with punctuation glued to text :: .w high all express in ly. if neglected, end which have now stood the test of public exp-</t>
+        </is>
+      </c>
       <c r="T17" s="1" t="inlineStr"/>
       <c r="U17" s="1" t="inlineStr"/>
       <c r="V17" s="1" t="inlineStr"/>
@@ -1877,19 +1893,19 @@
       </c>
       <c r="J18" s="1" t="inlineStr">
         <is>
-          <t>L830: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L830: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K18" s="1" t="inlineStr">
         <is>
-          <t>L285: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢information to be had on applying at the complaints, or from whom genuine European , ALICE Tell</t>
+          <t>L706: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: are so composed that disease within the range ©-</t>
         </is>
       </c>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L152: isolated marker/symbol line :: 0</t>
+          <t>L151: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -1900,11 +1916,15 @@
       <c r="P18" s="1" t="inlineStr"/>
       <c r="Q18" s="1" t="inlineStr">
         <is>
-          <t>L734: punctuation artifact: double/multiple hyphen :: e ------------------------ - - cures and directions</t>
+          <t>L840: punctuation artifact: double/multiple hyphen | suspicious token(s): Filma63 (letter/digit mix) :: -toneused the Filma63--a</t>
         </is>
       </c>
       <c r="R18" s="1" t="inlineStr"/>
-      <c r="S18" s="1" t="inlineStr"/>
+      <c r="S18" s="1" t="inlineStr">
+        <is>
+          <t>L1124: line starts with digit/letter garbage token | suspicious token(s): 1Wholesale (letter/digit mix) :: 1Wholesale and for Exportation by the</t>
+        </is>
+      </c>
       <c r="T18" s="1" t="inlineStr"/>
       <c r="U18" s="1" t="inlineStr"/>
       <c r="V18" s="1" t="inlineStr"/>
@@ -1936,19 +1956,19 @@
       </c>
       <c r="J19" s="1" t="inlineStr">
         <is>
-          <t>L836: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L836: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K19" s="1" t="inlineStr">
         <is>
-          <t>L289: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | punctuation artifact: double/multiple hyphen :: 1. C HART, Persons IN ANY PART OF THE WORLD â€¢ of -----</t>
+          <t>L791: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L153: isolated marker/symbol line :: X</t>
+          <t>L152: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -1959,7 +1979,7 @@
       <c r="P19" s="1" t="inlineStr"/>
       <c r="Q19" s="1" t="inlineStr">
         <is>
-          <t>L840: punctuation artifact: double/multiple hyphen | suspicious token(s): Filma63 (letter/digit mix) :: -toneused the Filma63--a</t>
+          <t>L912: punctuation artifact: repeated periods | missing space around punctuation :: .-.... teething, by softening the gums,reducing</t>
         </is>
       </c>
       <c r="R19" s="1" t="inlineStr"/>
@@ -1995,19 +2015,19 @@
       </c>
       <c r="J20" s="1" t="inlineStr">
         <is>
-          <t>L897: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L897: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K20" s="1" t="inlineStr">
         <is>
-          <t>L292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | line starts with punctuation glued to text :: _________________________â€” â€” correct detail of their cases witha remit-</t>
+          <t>L854: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L154: isolated marker/symbol line :: 1</t>
+          <t>L153: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -2018,7 +2038,7 @@
       <c r="P20" s="1" t="inlineStr"/>
       <c r="Q20" s="1" t="inlineStr">
         <is>
-          <t>L912: punctuation artifact: repeated periods | missing space around punctuation :: .-.... teething, by softening the gums,reducing</t>
+          <t>L916: punctuation artifact: repeated periods | suspicious token(s): theirSAUCE (odd internal casing) :: theirSAUCE is, LATE THE BOWELS..</t>
         </is>
       </c>
       <c r="R20" s="1" t="inlineStr"/>
@@ -2054,19 +2074,19 @@
       </c>
       <c r="J21" s="1" t="inlineStr">
         <is>
-          <t>L935: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L935: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K21" s="1" t="inlineStr">
         <is>
-          <t>L334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: every countryâ€”a record, the like</t>
+          <t>L886: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: use. When once tried, its superiority over €</t>
         </is>
       </c>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L171: isolated marker/symbol line :: 0</t>
+          <t>L154: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -2077,7 +2097,7 @@
       <c r="P21" s="1" t="inlineStr"/>
       <c r="Q21" s="1" t="inlineStr">
         <is>
-          <t>L916: punctuation artifact: repeated periods | suspicious token(s): theirSAUCE (odd internal casing) :: theirSAUCE is, LATE THE BOWELS..</t>
+          <t>L934: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: well know that diffe- •</t>
         </is>
       </c>
       <c r="R21" s="1" t="inlineStr"/>
@@ -2108,24 +2128,24 @@
       </c>
       <c r="I22" s="1" t="inlineStr">
         <is>
-          <t>L675: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): HalfRestorative (odd internal casing) :: minutes, if two or on the application ofâ€˜ourâ€™ HalfRestorativeâ€�</t>
+          <t>L675: suspicious token(s): HalfRestorative (odd internal casing) :: minutes, if two or on the application of‘our’ HalfRestorative”</t>
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr">
         <is>
-          <t>L950: stray/suspicious non-ASCII glyph(s): U+00A4 CURRENCY SIGN | isolated marker/symbol line :: å¤§</t>
+          <t>L950: stray/suspicious non-ASCII glyph(s): U+5927 CJK UNIFIED IDEOGRAPH-5927 | isolated marker/symbol line :: 大</t>
         </is>
       </c>
       <c r="K22" s="1" t="inlineStr">
         <is>
-          <t>L354: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: cimatest. Suman family has its origin directly don.â€� are discernable as a Water mark in</t>
+          <t>L929: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DR. J. €. AVER &amp; Co.</t>
         </is>
       </c>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L177: isolated marker/symbol line :: 4</t>
+          <t>L170: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -2136,7 +2156,7 @@
       <c r="P22" s="1" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr">
         <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: hyphen/bullet debris :: â€” â€” -**. DYSPEPSIA â€”No person with this distress-</t>
+          <t>L966: punctuation artifact: hyphen/bullet debris :: — — -**. DYSPEPSIA —No person with this distress-</t>
         </is>
       </c>
       <c r="R22" s="1" t="inlineStr"/>
@@ -2172,19 +2192,19 @@
       </c>
       <c r="J23" s="1" t="inlineStr">
         <is>
-          <t>L953: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: t Incorporate â€œThe College of Three</t>
+          <t>L960: stray/suspicious non-ASCII glyph(s): U+91CC CJK UNIFIED IDEOGRAPH-91CC | isolated marker/symbol line :: 里</t>
         </is>
       </c>
       <c r="K23" s="1" t="inlineStr">
         <is>
-          <t>L367: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: Such a medicine we supply in - -----â€”â€”</t>
+          <t>L934: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: well know that diffe- •</t>
         </is>
       </c>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L178: isolated marker/symbol line :: 0</t>
+          <t>L171: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -2221,7 +2241,7 @@
       <c r="G24" s="1" t="inlineStr"/>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>L653: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): A1001 (letter/digit mix) :: â€” A1001</t>
+          <t>L653: suspicious token(s): A1001 (letter/digit mix) :: — A1001</t>
         </is>
       </c>
       <c r="I24" s="1" t="inlineStr">
@@ -2231,19 +2251,19 @@
       </c>
       <c r="J24" s="1" t="inlineStr">
         <is>
-          <t>L994: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L994: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K24" s="1" t="inlineStr">
         <is>
-          <t>L369: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: AYERâ€™S</t>
+          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with © Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
         </is>
       </c>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L179: isolated marker/symbol line :: t</t>
+          <t>L177: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -2290,19 +2310,19 @@
       </c>
       <c r="J25" s="1" t="inlineStr">
         <is>
-          <t>L1154: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): T0 (letter/digit mix), coRv (odd internal casing) :: T0 coRv â€” Rivers</t>
+          <t>L1228: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
         </is>
       </c>
       <c r="K25" s="1" t="inlineStr">
         <is>
-          <t>L390: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1345: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L181: isolated marker/symbol line :: 4</t>
+          <t>L178: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -2349,19 +2369,15 @@
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
-          <t>L1257: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mercurial Diseases. â€” Never fad. to en</t>
-        </is>
-      </c>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L398: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ YS</t>
-        </is>
-      </c>
+          <t>L1229: stray/suspicious non-ASCII glyph(s): U+7F8E CJK UNIFIED IDEOGRAPH-7F8E :: R 美</t>
+        </is>
+      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L189: isolated marker/symbol line :: 2</t>
+          <t>L179: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2407,16 +2423,12 @@
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L424: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: it from the patientâ€™s system,</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L206: isolated marker/symbol line :: â†’</t>
+          <t>L181: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -2427,7 +2439,7 @@
       <c r="P27" s="1" t="inlineStr"/>
       <c r="Q27" s="1" t="inlineStr">
         <is>
-          <t>L1204: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€” anxious to make known to his fellow-suf- _______â€” ......</t>
+          <t>L1204: punctuation artifact: repeated periods :: — anxious to make known to his fellow-suf- _______— ......</t>
         </is>
       </c>
       <c r="R27" s="1" t="inlineStr"/>
@@ -2458,20 +2470,16 @@
       </c>
       <c r="I28" s="1" t="inlineStr">
         <is>
-          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with Â© Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
+          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with © Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L442: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Hollowayâ€™s Pills are the best remedy</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L218: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L187: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2513,16 +2521,12 @@
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L443: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: known in the world for theâ€¢</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L298: isolated marker/symbol line :: 8</t>
+          <t>L189: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
@@ -2560,16 +2564,12 @@
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L506: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN, U+2122 TRADE MARK SIGN :: â€¢ Hair Restorativeâ€™ which he liked very much</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L310: isolated marker/symbol line :: 8</t>
+          <t>L206: stray/suspicious non-ASCII glyph(s): U+2192 RIGHTWARDS ARROW | isolated marker/symbol line :: →</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -2607,16 +2607,12 @@
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L556: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: and SKIN DISEASES, Sr. ANTHONYâ€™S FIRE,</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L311: isolated marker/symbol line :: S</t>
+          <t>L218: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
@@ -2645,7 +2641,7 @@
       <c r="G32" s="1" t="inlineStr"/>
       <c r="H32" s="1" t="inlineStr">
         <is>
-          <t>L804: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): grDB (odd internal casing) :: CAUTIONâ€” X e grDB nless</t>
+          <t>L804: suspicious token(s): grDB (odd internal casing) :: CAUTION— X e grDB nless</t>
         </is>
       </c>
       <c r="I32" s="1" t="inlineStr">
@@ -2654,21 +2650,17 @@
         </is>
       </c>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L569: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Fever &amp; Ague.â€”</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L312: isolated marker/symbol line :: 4</t>
+          <t>L298: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L1345: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1345: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -2701,16 +2693,12 @@
         </is>
       </c>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L601: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: â‚¬holers Infantum You can sell a great deal of your Hair Resto-</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L313: isolated marker/symbol line :: 1</t>
+          <t>L299: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心 '</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
@@ -2748,16 +2736,12 @@
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L607: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: in ** impurity of the bloodâ€� is founded m</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L325: isolated marker/symbol line :: a</t>
+          <t>L310: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr">
@@ -2791,20 +2775,16 @@
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
-          <t>L1292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): SEALdo (odd internal casing) :: U PALE SEALdo.â€” 25 barrels very fine,</t>
+          <t>L1292: suspicious token(s): SEALdo (odd internal casing) :: U PALE SEALdo.— 25 barrels very fine,</t>
         </is>
       </c>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L618: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: F CAUTION â€” None are genuine unless</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L328: isolated marker/symbol line :: H</t>
+          <t>L311: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr">
@@ -2842,16 +2822,12 @@
         </is>
       </c>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L645: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ayerâ€™s Cathartic Pills, dose must be</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L329: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L312: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr">
@@ -2885,16 +2861,12 @@
       </c>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L649: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: dividual taking itâ€¢</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L334: isolated marker/symbol line :: H</t>
+          <t>L313: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr">
@@ -2928,16 +2900,12 @@
       </c>
       <c r="I38" s="1" t="inlineStr"/>
       <c r="J38" s="1" t="inlineStr"/>
-      <c r="K38" s="1" t="inlineStr">
-        <is>
-          <t>L652: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gently on the Bowel- Â©</t>
-        </is>
-      </c>
+      <c r="K38" s="1" t="inlineStr"/>
       <c r="L38" s="1" t="inlineStr"/>
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L335: isolated marker/symbol line :: 4</t>
+          <t>L325: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr">
@@ -2971,16 +2939,12 @@
       </c>
       <c r="I39" s="1" t="inlineStr"/>
       <c r="J39" s="1" t="inlineStr"/>
-      <c r="K39" s="1" t="inlineStr">
-        <is>
-          <t>L673: stray/suspicious non-ASCII glyph(s): U+00A2 CENT SIGN :: â„¢ thousands can about the time of my arrival in the United</t>
-        </is>
-      </c>
+      <c r="K39" s="1" t="inlineStr"/>
       <c r="L39" s="1" t="inlineStr"/>
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L337: isolated marker/symbol line :: P.</t>
+          <t>L328: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -3010,16 +2974,12 @@
       </c>
       <c r="I40" s="1" t="inlineStr"/>
       <c r="J40" s="1" t="inlineStr"/>
-      <c r="K40" s="1" t="inlineStr">
-        <is>
-          <t>L675: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE, U+2122 TRADE MARK SIGN, U+FFFD REPLACEMENT CHARACTER | suspicious token(s): HalfRestorative (odd internal casing) :: minutes, if two or on the application ofâ€˜ourâ€™ HalfRestorativeâ€�</t>
-        </is>
-      </c>
+      <c r="K40" s="1" t="inlineStr"/>
       <c r="L40" s="1" t="inlineStr"/>
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L342: isolated marker/symbol line :: N</t>
+          <t>L329: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -3049,16 +3009,12 @@
       </c>
       <c r="I41" s="1" t="inlineStr"/>
       <c r="J41" s="1" t="inlineStr"/>
-      <c r="K41" s="1" t="inlineStr">
-        <is>
-          <t>L700: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ â€¢ Sold at the Manufactories of Professor</t>
-        </is>
-      </c>
+      <c r="K41" s="1" t="inlineStr"/>
       <c r="L41" s="1" t="inlineStr"/>
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L343: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
+          <t>L333: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -3088,16 +3044,12 @@
       </c>
       <c r="I42" s="1" t="inlineStr"/>
       <c r="J42" s="1" t="inlineStr"/>
-      <c r="K42" s="1" t="inlineStr">
-        <is>
-          <t>L706: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: are so composed that disease within the range Â©-</t>
-        </is>
-      </c>
+      <c r="K42" s="1" t="inlineStr"/>
       <c r="L42" s="1" t="inlineStr"/>
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L344: isolated marker/symbol line :: 1</t>
+          <t>L334: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -3127,16 +3079,12 @@
       </c>
       <c r="I43" s="1" t="inlineStr"/>
       <c r="J43" s="1" t="inlineStr"/>
-      <c r="K43" s="1" t="inlineStr">
-        <is>
-          <t>L750: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: N B â€” Directions for the guidance of pa-</t>
-        </is>
-      </c>
+      <c r="K43" s="1" t="inlineStr"/>
       <c r="L43" s="1" t="inlineStr"/>
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L345: isolated marker/symbol line :: e</t>
+          <t>L335: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -3166,16 +3114,12 @@
       </c>
       <c r="I44" s="1" t="inlineStr"/>
       <c r="J44" s="1" t="inlineStr"/>
-      <c r="K44" s="1" t="inlineStr">
-        <is>
-          <t>L791: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: Â©</t>
-        </is>
-      </c>
+      <c r="K44" s="1" t="inlineStr"/>
       <c r="L44" s="1" t="inlineStr"/>
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L346: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L337: isolated marker/symbol line :: P.</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -3205,16 +3149,12 @@
       </c>
       <c r="I45" s="1" t="inlineStr"/>
       <c r="J45" s="1" t="inlineStr"/>
-      <c r="K45" s="1" t="inlineStr">
-        <is>
-          <t>L793: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: MOFFATâ€™S</t>
-        </is>
-      </c>
+      <c r="K45" s="1" t="inlineStr"/>
       <c r="L45" s="1" t="inlineStr"/>
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L347: isolated marker/symbol line :: m</t>
+          <t>L342: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -3244,16 +3184,12 @@
       </c>
       <c r="I46" s="1" t="inlineStr"/>
       <c r="J46" s="1" t="inlineStr"/>
-      <c r="K46" s="1" t="inlineStr">
-        <is>
-          <t>L826: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: KEATINGâ€™S</t>
-        </is>
-      </c>
+      <c r="K46" s="1" t="inlineStr"/>
       <c r="L46" s="1" t="inlineStr"/>
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L348: isolated marker/symbol line :: 9</t>
+          <t>L343: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | isolated marker/symbol line :: ©</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -3283,16 +3219,12 @@
       </c>
       <c r="I47" s="1" t="inlineStr"/>
       <c r="J47" s="1" t="inlineStr"/>
-      <c r="K47" s="1" t="inlineStr">
-        <is>
-          <t>L839: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: I creasing demand / ness. Pain and Sore and other constitutic naâ€˜ derangements. The</t>
-        </is>
-      </c>
+      <c r="K47" s="1" t="inlineStr"/>
       <c r="L47" s="1" t="inlineStr"/>
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L363: isolated marker/symbol line :: 000</t>
+          <t>L344: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -3322,16 +3254,12 @@
       </c>
       <c r="I48" s="1" t="inlineStr"/>
       <c r="J48" s="1" t="inlineStr"/>
-      <c r="K48" s="1" t="inlineStr">
-        <is>
-          <t>L854: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K48" s="1" t="inlineStr"/>
       <c r="L48" s="1" t="inlineStr"/>
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L365: isolated marker/symbol line :: 0</t>
+          <t>L345: isolated marker/symbol line :: e</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -3361,16 +3289,12 @@
       </c>
       <c r="I49" s="1" t="inlineStr"/>
       <c r="J49" s="1" t="inlineStr"/>
-      <c r="K49" s="1" t="inlineStr">
-        <is>
-          <t>L878: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Complaints.â€”la the south and west, where</t>
-        </is>
-      </c>
+      <c r="K49" s="1" t="inlineStr"/>
       <c r="L49" s="1" t="inlineStr"/>
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L366: isolated marker/symbol line :: 2</t>
+          <t>L346: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -3400,16 +3324,12 @@
       </c>
       <c r="I50" s="1" t="inlineStr"/>
       <c r="J50" s="1" t="inlineStr"/>
-      <c r="K50" s="1" t="inlineStr">
-        <is>
-          <t>L886: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: use. When once tried, its superiority over â‚¬</t>
-        </is>
-      </c>
+      <c r="K50" s="1" t="inlineStr"/>
       <c r="L50" s="1" t="inlineStr"/>
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L367: symbol-only separator/garbage line :: $400, 000.</t>
+          <t>L347: isolated marker/symbol line :: m</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -3439,16 +3359,12 @@
       </c>
       <c r="I51" s="1" t="inlineStr"/>
       <c r="J51" s="1" t="inlineStr"/>
-      <c r="K51" s="1" t="inlineStr">
-        <is>
-          <t>L914: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Tell LEA &amp; all inflammationâ€”will allay ALL PAIN and</t>
-        </is>
-      </c>
+      <c r="K51" s="1" t="inlineStr"/>
       <c r="L51" s="1" t="inlineStr"/>
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L371: isolated marker/symbol line :: X</t>
+          <t>L348: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -3478,16 +3394,12 @@
       </c>
       <c r="I52" s="1" t="inlineStr"/>
       <c r="J52" s="1" t="inlineStr"/>
-      <c r="K52" s="1" t="inlineStr">
-        <is>
-          <t>L929: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: DR. J. â‚¬. AVER &amp; Co.</t>
-        </is>
-      </c>
+      <c r="K52" s="1" t="inlineStr"/>
       <c r="L52" s="1" t="inlineStr"/>
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L372: isolated marker/symbol line :: %</t>
+          <t>L363: isolated marker/symbol line :: 000</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -3517,16 +3429,12 @@
       </c>
       <c r="I53" s="1" t="inlineStr"/>
       <c r="J53" s="1" t="inlineStr"/>
-      <c r="K53" s="1" t="inlineStr">
-        <is>
-          <t>L934: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: well know that diffe- â€¢</t>
-        </is>
-      </c>
+      <c r="K53" s="1" t="inlineStr"/>
       <c r="L53" s="1" t="inlineStr"/>
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L417: symbol-only separator/garbage line :: 1851.</t>
+          <t>L365: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -3556,16 +3464,12 @@
       </c>
       <c r="I54" s="1" t="inlineStr"/>
       <c r="J54" s="1" t="inlineStr"/>
-      <c r="K54" s="1" t="inlineStr">
-        <is>
-          <t>L939: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: The Family Ca E Children or Adults, mist &amp;c. No. 19. St. Paulâ€™s Church Yard,</t>
-        </is>
-      </c>
+      <c r="K54" s="1" t="inlineStr"/>
       <c r="L54" s="1" t="inlineStr"/>
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L422: isolated marker/symbol line :: 4</t>
+          <t>L366: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -3595,16 +3499,12 @@
       </c>
       <c r="I55" s="1" t="inlineStr"/>
       <c r="J55" s="1" t="inlineStr"/>
-      <c r="K55" s="1" t="inlineStr">
-        <is>
-          <t>L940: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN | suspicious token(s): thartiePill (odd internal casing) | missing space around punctuation :: thartiePill has,with Â© Rheumatism, a great | I London. Sold retail by all Druggists and Pa-</t>
-        </is>
-      </c>
+      <c r="K55" s="1" t="inlineStr"/>
       <c r="L55" s="1" t="inlineStr"/>
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L424: isolated marker/symbol line :: ?</t>
+          <t>L367: symbol-only separator/garbage line :: $400, 000.</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -3634,16 +3534,12 @@
       </c>
       <c r="I56" s="1" t="inlineStr"/>
       <c r="J56" s="1" t="inlineStr"/>
-      <c r="K56" s="1" t="inlineStr">
-        <is>
-          <t>L942: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: well established fact, and many diseases to N. B â€”To prevent spurious imitations</t>
-        </is>
-      </c>
+      <c r="K56" s="1" t="inlineStr"/>
       <c r="L56" s="1" t="inlineStr"/>
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L425: isolated marker/symbol line :: A</t>
+          <t>L371: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -3668,21 +3564,17 @@
       <c r="G57" s="1" t="inlineStr"/>
       <c r="H57" s="1" t="inlineStr">
         <is>
-          <t>L1154: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): T0 (letter/digit mix), coRv (odd internal casing) :: T0 coRv â€” Rivers</t>
+          <t>L1154: suspicious token(s): T0 (letter/digit mix), coRv (odd internal casing) :: T0 coRv — Rivers</t>
         </is>
       </c>
       <c r="I57" s="1" t="inlineStr"/>
       <c r="J57" s="1" t="inlineStr"/>
-      <c r="K57" s="1" t="inlineStr">
-        <is>
-          <t>L944: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: been compounded which Beth isheir, please observe that the words, KEATINGâ€™S</t>
-        </is>
-      </c>
+      <c r="K57" s="1" t="inlineStr"/>
       <c r="L57" s="1" t="inlineStr"/>
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L462: isolated marker/symbol line :: +</t>
+          <t>L372: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -3712,16 +3604,12 @@
       </c>
       <c r="I58" s="1" t="inlineStr"/>
       <c r="J58" s="1" t="inlineStr"/>
-      <c r="K58" s="1" t="inlineStr">
-        <is>
-          <t>L966: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: hyphen/bullet debris :: â€” â€” -**. DYSPEPSIA â€”No person with this distress-</t>
-        </is>
-      </c>
+      <c r="K58" s="1" t="inlineStr"/>
       <c r="L58" s="1" t="inlineStr"/>
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L510: isolated marker/symbol line :: 0</t>
+          <t>L417: symbol-only separator/garbage line :: 1851.</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3751,16 +3639,12 @@
       </c>
       <c r="I59" s="1" t="inlineStr"/>
       <c r="J59" s="1" t="inlineStr"/>
-      <c r="K59" s="1" t="inlineStr">
-        <is>
-          <t>L982: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” WORCESTERSHIRE SAUCE," the la-</t>
-        </is>
-      </c>
+      <c r="K59" s="1" t="inlineStr"/>
       <c r="L59" s="1" t="inlineStr"/>
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L523: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‹</t>
+          <t>L422: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -3790,16 +3674,12 @@
       </c>
       <c r="I60" s="1" t="inlineStr"/>
       <c r="J60" s="1" t="inlineStr"/>
-      <c r="K60" s="1" t="inlineStr">
-        <is>
-          <t>L993: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Ladiesâ€™</t>
-        </is>
-      </c>
+      <c r="K60" s="1" t="inlineStr"/>
       <c r="L60" s="1" t="inlineStr"/>
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L524: isolated marker/symbol line :: Y</t>
+          <t>L424: isolated marker/symbol line :: ?</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -3829,16 +3709,12 @@
       </c>
       <c r="I61" s="1" t="inlineStr"/>
       <c r="J61" s="1" t="inlineStr"/>
-      <c r="K61" s="1" t="inlineStr">
-        <is>
-          <t>L1007: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: system subject to a return of the diseaseâ€”</t>
-        </is>
-      </c>
+      <c r="K61" s="1" t="inlineStr"/>
       <c r="L61" s="1" t="inlineStr"/>
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L556: isolated marker/symbol line :: 3</t>
+          <t>L425: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -3868,16 +3744,12 @@
       </c>
       <c r="I62" s="1" t="inlineStr"/>
       <c r="J62" s="1" t="inlineStr"/>
-      <c r="K62" s="1" t="inlineStr">
-        <is>
-          <t>L1008: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: a cure by these medicines is permanent.â€”</t>
-        </is>
-      </c>
+      <c r="K62" s="1" t="inlineStr"/>
       <c r="L62" s="1" t="inlineStr"/>
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L557: isolated marker/symbol line :: 4</t>
+          <t>L462: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -3907,16 +3779,12 @@
       </c>
       <c r="I63" s="1" t="inlineStr"/>
       <c r="J63" s="1" t="inlineStr"/>
-      <c r="K63" s="1" t="inlineStr">
-        <is>
-          <t>L1011: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: MERCURAL DISEASES â€”Never fails to era-</t>
-        </is>
-      </c>
+      <c r="K63" s="1" t="inlineStr"/>
       <c r="L63" s="1" t="inlineStr"/>
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L558: isolated marker/symbol line :: 4</t>
+          <t>L482: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3946,16 +3814,12 @@
       </c>
       <c r="I64" s="1" t="inlineStr"/>
       <c r="J64" s="1" t="inlineStr"/>
-      <c r="K64" s="1" t="inlineStr">
-        <is>
-          <t>L1028: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: of Keelingâ€™s Cough Lozenges is re-</t>
-        </is>
-      </c>
+      <c r="K64" s="1" t="inlineStr"/>
       <c r="L64" s="1" t="inlineStr"/>
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L564: isolated marker/symbol line :: å››</t>
+          <t>L510: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3985,16 +3849,12 @@
       </c>
       <c r="I65" s="1" t="inlineStr"/>
       <c r="J65" s="1" t="inlineStr"/>
-      <c r="K65" s="1" t="inlineStr">
-        <is>
-          <t>L1041: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: No. I Gibâ€™</t>
-        </is>
-      </c>
+      <c r="K65" s="1" t="inlineStr"/>
       <c r="L65" s="1" t="inlineStr"/>
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L569: isolated marker/symbol line :: 1</t>
+          <t>L523: isolated marker/symbol line :: 》</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -4024,16 +3884,12 @@
       </c>
       <c r="I66" s="1" t="inlineStr"/>
       <c r="J66" s="1" t="inlineStr"/>
-      <c r="K66" s="1" t="inlineStr">
-        <is>
-          <t>L1092: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SIR.â€”Thevery excellent properties of your</t>
-        </is>
-      </c>
+      <c r="K66" s="1" t="inlineStr"/>
       <c r="L66" s="1" t="inlineStr"/>
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L571: isolated marker/symbol line :: 4</t>
+          <t>L524: isolated marker/symbol line :: Y</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -4063,16 +3919,12 @@
       </c>
       <c r="I67" s="1" t="inlineStr"/>
       <c r="J67" s="1" t="inlineStr"/>
-      <c r="K67" s="1" t="inlineStr">
-        <is>
-          <t>L1099: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Palpitation of the Heart, Painterâ€™s Cholic.</t>
-        </is>
-      </c>
+      <c r="K67" s="1" t="inlineStr"/>
       <c r="L67" s="1" t="inlineStr"/>
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L583: isolated marker/symbol line :: t</t>
+          <t>L556: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -4102,16 +3954,12 @@
       </c>
       <c r="I68" s="1" t="inlineStr"/>
       <c r="J68" s="1" t="inlineStr"/>
-      <c r="K68" s="1" t="inlineStr">
-        <is>
-          <t>L1101: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PILES â€”The original Proprietor of these</t>
-        </is>
-      </c>
+      <c r="K68" s="1" t="inlineStr"/>
       <c r="L68" s="1" t="inlineStr"/>
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L592: isolated marker/symbol line :: .</t>
+          <t>L557: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -4141,16 +3989,12 @@
       </c>
       <c r="I69" s="1" t="inlineStr"/>
       <c r="J69" s="1" t="inlineStr"/>
-      <c r="K69" s="1" t="inlineStr">
-        <is>
-          <t>L1116: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: yoursâ€”even one of them will check the most</t>
-        </is>
-      </c>
+      <c r="K69" s="1" t="inlineStr"/>
       <c r="L69" s="1" t="inlineStr"/>
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L634: isolated marker/symbol line :: 10</t>
+          <t>L558: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -4180,16 +4024,12 @@
       </c>
       <c r="I70" s="1" t="inlineStr"/>
       <c r="J70" s="1" t="inlineStr"/>
-      <c r="K70" s="1" t="inlineStr">
-        <is>
-          <t>L1148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: TO CONSUMPTIVES â€” The advertiser</t>
-        </is>
-      </c>
+      <c r="K70" s="1" t="inlineStr"/>
       <c r="L70" s="1" t="inlineStr"/>
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L642: isolated marker/symbol line :: 2</t>
+          <t>L564: stray/suspicious non-ASCII glyph(s): U+56DB CJK UNIFIED IDEOGRAPH-56DB | isolated marker/symbol line :: 四</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -4219,16 +4059,12 @@
       </c>
       <c r="I71" s="1" t="inlineStr"/>
       <c r="J71" s="1" t="inlineStr"/>
-      <c r="K71" s="1" t="inlineStr">
-        <is>
-          <t>L1204: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: repeated periods :: â€” anxious to make known to his fellow-suf- _______â€” ......</t>
-        </is>
-      </c>
+      <c r="K71" s="1" t="inlineStr"/>
       <c r="L71" s="1" t="inlineStr"/>
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L643: isolated marker/symbol line :: " 0</t>
+          <t>L569: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -4258,16 +4094,12 @@
       </c>
       <c r="I72" s="1" t="inlineStr"/>
       <c r="J72" s="1" t="inlineStr"/>
-      <c r="K72" s="1" t="inlineStr">
-        <is>
-          <t>L1291: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ASPE COD OILâ€”100 bbls. Ex. Choice.</t>
-        </is>
-      </c>
+      <c r="K72" s="1" t="inlineStr"/>
       <c r="L72" s="1" t="inlineStr"/>
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L644: isolated marker/symbol line :: -</t>
+          <t>L571: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -4297,16 +4129,12 @@
       </c>
       <c r="I73" s="1" t="inlineStr"/>
       <c r="J73" s="1" t="inlineStr"/>
-      <c r="K73" s="1" t="inlineStr">
-        <is>
-          <t>L1292: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | suspicious token(s): SEALdo (odd internal casing) :: U PALE SEALdo.â€” 25 barrels very fine,</t>
-        </is>
-      </c>
+      <c r="K73" s="1" t="inlineStr"/>
       <c r="L73" s="1" t="inlineStr"/>
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L651: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L583: isolated marker/symbol line :: t</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -4336,16 +4164,12 @@
       </c>
       <c r="I74" s="1" t="inlineStr"/>
       <c r="J74" s="1" t="inlineStr"/>
-      <c r="K74" s="1" t="inlineStr">
-        <is>
-          <t>L1310: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: lug child and the relief will be SUREâ€”yes.</t>
-        </is>
-      </c>
+      <c r="K74" s="1" t="inlineStr"/>
       <c r="L74" s="1" t="inlineStr"/>
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L655: isolated marker/symbol line :: 7</t>
+          <t>L592: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -4371,16 +4195,12 @@
       <c r="H75" s="1" t="inlineStr"/>
       <c r="I75" s="1" t="inlineStr"/>
       <c r="J75" s="1" t="inlineStr"/>
-      <c r="K75" s="1" t="inlineStr">
-        <is>
-          <t>L1311: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ABSOLUTELY SUREâ€”to follow the use of</t>
-        </is>
-      </c>
+      <c r="K75" s="1" t="inlineStr"/>
       <c r="L75" s="1" t="inlineStr"/>
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L656: isolated marker/symbol line :: 1</t>
+          <t>L634: isolated marker/symbol line :: 10</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -4406,16 +4226,12 @@
       <c r="H76" s="1" t="inlineStr"/>
       <c r="I76" s="1" t="inlineStr"/>
       <c r="J76" s="1" t="inlineStr"/>
-      <c r="K76" s="1" t="inlineStr">
-        <is>
-          <t>L1329: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: Nâ€œ Scottsâ€� Brand, Choice,</t>
-        </is>
-      </c>
+      <c r="K76" s="1" t="inlineStr"/>
       <c r="L76" s="1" t="inlineStr"/>
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L657: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L642: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr"/>
@@ -4441,16 +4257,12 @@
       <c r="H77" s="1" t="inlineStr"/>
       <c r="I77" s="1" t="inlineStr"/>
       <c r="J77" s="1" t="inlineStr"/>
-      <c r="K77" s="1" t="inlineStr">
-        <is>
-          <t>L1334: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: GENERAL ASSORTMENT.â€”For Sale</t>
-        </is>
-      </c>
+      <c r="K77" s="1" t="inlineStr"/>
       <c r="L77" s="1" t="inlineStr"/>
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L676: isolated marker/symbol line :: m</t>
+          <t>L643: isolated marker/symbol line :: " 0</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr"/>
@@ -4476,16 +4288,12 @@
       <c r="H78" s="1" t="inlineStr"/>
       <c r="I78" s="1" t="inlineStr"/>
       <c r="J78" s="1" t="inlineStr"/>
-      <c r="K78" s="1" t="inlineStr">
-        <is>
-          <t>L1340: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: DVASS,â€”</t>
-        </is>
-      </c>
+      <c r="K78" s="1" t="inlineStr"/>
       <c r="L78" s="1" t="inlineStr"/>
       <c r="M78" s="1" t="inlineStr"/>
       <c r="N78" s="1" t="inlineStr">
         <is>
-          <t>L734: isolated marker/symbol line :: 4</t>
+          <t>L644: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O78" s="1" t="inlineStr"/>
@@ -4511,16 +4319,12 @@
       <c r="H79" s="1" t="inlineStr"/>
       <c r="I79" s="1" t="inlineStr"/>
       <c r="J79" s="1" t="inlineStr"/>
-      <c r="K79" s="1" t="inlineStr">
-        <is>
-          <t>L1345: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K79" s="1" t="inlineStr"/>
       <c r="L79" s="1" t="inlineStr"/>
       <c r="M79" s="1" t="inlineStr"/>
       <c r="N79" s="1" t="inlineStr">
         <is>
-          <t>L747: isolated marker/symbol line :: 4</t>
+          <t>L651: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O79" s="1" t="inlineStr"/>
@@ -4551,7 +4355,7 @@
       <c r="M80" s="1" t="inlineStr"/>
       <c r="N80" s="1" t="inlineStr">
         <is>
-          <t>L770: isolated marker/symbol line :: A</t>
+          <t>L655: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O80" s="1" t="inlineStr"/>
@@ -4582,7 +4386,7 @@
       <c r="M81" s="1" t="inlineStr"/>
       <c r="N81" s="1" t="inlineStr">
         <is>
-          <t>L800: isolated marker/symbol line :: P</t>
+          <t>L656: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O81" s="1" t="inlineStr"/>
@@ -4613,7 +4417,7 @@
       <c r="M82" s="1" t="inlineStr"/>
       <c r="N82" s="1" t="inlineStr">
         <is>
-          <t>L830: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L657: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O82" s="1" t="inlineStr"/>
@@ -4644,7 +4448,7 @@
       <c r="M83" s="1" t="inlineStr"/>
       <c r="N83" s="1" t="inlineStr">
         <is>
-          <t>L831: isolated marker/symbol line :: 1.</t>
+          <t>L676: isolated marker/symbol line :: m</t>
         </is>
       </c>
       <c r="O83" s="1" t="inlineStr"/>
@@ -4675,7 +4479,7 @@
       <c r="M84" s="1" t="inlineStr"/>
       <c r="N84" s="1" t="inlineStr">
         <is>
-          <t>L832: isolated marker/symbol line :: 7</t>
+          <t>L734: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O84" s="1" t="inlineStr"/>
@@ -4706,7 +4510,7 @@
       <c r="M85" s="1" t="inlineStr"/>
       <c r="N85" s="1" t="inlineStr">
         <is>
-          <t>L835: isolated marker/symbol line :: A</t>
+          <t>L747: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O85" s="1" t="inlineStr"/>
@@ -4737,7 +4541,7 @@
       <c r="M86" s="1" t="inlineStr"/>
       <c r="N86" s="1" t="inlineStr">
         <is>
-          <t>L836: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L770: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O86" s="1" t="inlineStr"/>
@@ -4768,7 +4572,7 @@
       <c r="M87" s="1" t="inlineStr"/>
       <c r="N87" s="1" t="inlineStr">
         <is>
-          <t>L839: isolated marker/symbol line :: 2</t>
+          <t>L800: isolated marker/symbol line :: P</t>
         </is>
       </c>
       <c r="O87" s="1" t="inlineStr"/>
@@ -4799,7 +4603,7 @@
       <c r="M88" s="1" t="inlineStr"/>
       <c r="N88" s="1" t="inlineStr">
         <is>
-          <t>L853: isolated marker/symbol line :: ,</t>
+          <t>L830: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O88" s="1" t="inlineStr"/>
@@ -4830,7 +4634,7 @@
       <c r="M89" s="1" t="inlineStr"/>
       <c r="N89" s="1" t="inlineStr">
         <is>
-          <t>L865: isolated marker/symbol line :: 20</t>
+          <t>L831: isolated marker/symbol line :: 1.</t>
         </is>
       </c>
       <c r="O89" s="1" t="inlineStr"/>
@@ -4861,7 +4665,7 @@
       <c r="M90" s="1" t="inlineStr"/>
       <c r="N90" s="1" t="inlineStr">
         <is>
-          <t>L884: isolated marker/symbol line :: H</t>
+          <t>L832: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O90" s="1" t="inlineStr"/>
@@ -4892,7 +4696,7 @@
       <c r="M91" s="1" t="inlineStr"/>
       <c r="N91" s="1" t="inlineStr">
         <is>
-          <t>L896: isolated marker/symbol line :: 3</t>
+          <t>L835: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O91" s="1" t="inlineStr"/>
@@ -4923,7 +4727,7 @@
       <c r="M92" s="1" t="inlineStr"/>
       <c r="N92" s="1" t="inlineStr">
         <is>
-          <t>L897: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L836: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O92" s="1" t="inlineStr"/>
@@ -4954,7 +4758,7 @@
       <c r="M93" s="1" t="inlineStr"/>
       <c r="N93" s="1" t="inlineStr">
         <is>
-          <t>L898: isolated marker/symbol line :: 1</t>
+          <t>L839: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O93" s="1" t="inlineStr"/>
@@ -4985,7 +4789,7 @@
       <c r="M94" s="1" t="inlineStr"/>
       <c r="N94" s="1" t="inlineStr">
         <is>
-          <t>L916: isolated marker/symbol line :: L.</t>
+          <t>L853: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O94" s="1" t="inlineStr"/>
@@ -5016,7 +4820,7 @@
       <c r="M95" s="1" t="inlineStr"/>
       <c r="N95" s="1" t="inlineStr">
         <is>
-          <t>L934: isolated marker/symbol line :: 2</t>
+          <t>L865: isolated marker/symbol line :: 20</t>
         </is>
       </c>
       <c r="O95" s="1" t="inlineStr"/>
@@ -5047,7 +4851,7 @@
       <c r="M96" s="1" t="inlineStr"/>
       <c r="N96" s="1" t="inlineStr">
         <is>
-          <t>L935: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L884: isolated marker/symbol line :: H</t>
         </is>
       </c>
       <c r="O96" s="1" t="inlineStr"/>
@@ -5078,7 +4882,7 @@
       <c r="M97" s="1" t="inlineStr"/>
       <c r="N97" s="1" t="inlineStr">
         <is>
-          <t>L941: isolated marker/symbol line :: N</t>
+          <t>L896: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O97" s="1" t="inlineStr"/>
@@ -5109,7 +4913,7 @@
       <c r="M98" s="1" t="inlineStr"/>
       <c r="N98" s="1" t="inlineStr">
         <is>
-          <t>L950: stray/suspicious non-ASCII glyph(s): U+00A4 CURRENCY SIGN | isolated marker/symbol line :: å¤§</t>
+          <t>L897: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="O98" s="1" t="inlineStr"/>
@@ -5140,7 +4944,7 @@
       <c r="M99" s="1" t="inlineStr"/>
       <c r="N99" s="1" t="inlineStr">
         <is>
-          <t>L956: isolated marker/symbol line :: B</t>
+          <t>L898: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O99" s="1" t="inlineStr"/>
@@ -5171,7 +4975,7 @@
       <c r="M100" s="1" t="inlineStr"/>
       <c r="N100" s="1" t="inlineStr">
         <is>
-          <t>L959: isolated marker/symbol line :: 2</t>
+          <t>L916: isolated marker/symbol line :: L.</t>
         </is>
       </c>
       <c r="O100" s="1" t="inlineStr"/>
@@ -5202,7 +5006,7 @@
       <c r="M101" s="1" t="inlineStr"/>
       <c r="N101" s="1" t="inlineStr">
         <is>
-          <t>L962: isolated marker/symbol line :: ?</t>
+          <t>L934: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O101" s="1" t="inlineStr"/>
@@ -5233,7 +5037,7 @@
       <c r="M102" s="1" t="inlineStr"/>
       <c r="N102" s="1" t="inlineStr">
         <is>
-          <t>L984: isolated marker/symbol line :: f</t>
+          <t>L935: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O102" s="1" t="inlineStr"/>
@@ -5264,7 +5068,7 @@
       <c r="M103" s="1" t="inlineStr"/>
       <c r="N103" s="1" t="inlineStr">
         <is>
-          <t>L986: isolated marker/symbol line :: -</t>
+          <t>L941: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O103" s="1" t="inlineStr"/>
@@ -5295,7 +5099,7 @@
       <c r="M104" s="1" t="inlineStr"/>
       <c r="N104" s="1" t="inlineStr">
         <is>
-          <t>L992: isolated marker/symbol line :: R</t>
+          <t>L950: stray/suspicious non-ASCII glyph(s): U+5927 CJK UNIFIED IDEOGRAPH-5927 | isolated marker/symbol line :: 大</t>
         </is>
       </c>
       <c r="O104" s="1" t="inlineStr"/>
@@ -5326,7 +5130,7 @@
       <c r="M105" s="1" t="inlineStr"/>
       <c r="N105" s="1" t="inlineStr">
         <is>
-          <t>L993: isolated marker/symbol line :: a</t>
+          <t>L956: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O105" s="1" t="inlineStr"/>
@@ -5357,7 +5161,7 @@
       <c r="M106" s="1" t="inlineStr"/>
       <c r="N106" s="1" t="inlineStr">
         <is>
-          <t>L994: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L959: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O106" s="1" t="inlineStr"/>
@@ -5388,7 +5192,7 @@
       <c r="M107" s="1" t="inlineStr"/>
       <c r="N107" s="1" t="inlineStr">
         <is>
-          <t>L995: isolated marker/symbol line :: .</t>
+          <t>L960: stray/suspicious non-ASCII glyph(s): U+91CC CJK UNIFIED IDEOGRAPH-91CC | isolated marker/symbol line :: 里</t>
         </is>
       </c>
       <c r="O107" s="1" t="inlineStr"/>
@@ -5419,7 +5223,7 @@
       <c r="M108" s="1" t="inlineStr"/>
       <c r="N108" s="1" t="inlineStr">
         <is>
-          <t>L1002: isolated marker/symbol line :: o</t>
+          <t>L962: isolated marker/symbol line :: ?</t>
         </is>
       </c>
       <c r="O108" s="1" t="inlineStr"/>
@@ -5450,7 +5254,7 @@
       <c r="M109" s="1" t="inlineStr"/>
       <c r="N109" s="1" t="inlineStr">
         <is>
-          <t>L1006: isolated marker/symbol line :: p</t>
+          <t>L984: isolated marker/symbol line :: f</t>
         </is>
       </c>
       <c r="O109" s="1" t="inlineStr"/>
@@ -5481,7 +5285,7 @@
       <c r="M110" s="1" t="inlineStr"/>
       <c r="N110" s="1" t="inlineStr">
         <is>
-          <t>L1016: isolated marker/symbol line :: p</t>
+          <t>L986: isolated marker/symbol line :: -</t>
         </is>
       </c>
       <c r="O110" s="1" t="inlineStr"/>
@@ -5512,7 +5316,7 @@
       <c r="M111" s="1" t="inlineStr"/>
       <c r="N111" s="1" t="inlineStr">
         <is>
-          <t>L1045: isolated marker/symbol line :: 2</t>
+          <t>L992: isolated marker/symbol line :: R</t>
         </is>
       </c>
       <c r="O111" s="1" t="inlineStr"/>
@@ -5543,7 +5347,7 @@
       <c r="M112" s="1" t="inlineStr"/>
       <c r="N112" s="1" t="inlineStr">
         <is>
-          <t>L1047: isolated marker/symbol line :: 1</t>
+          <t>L993: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O112" s="1" t="inlineStr"/>
@@ -5574,7 +5378,7 @@
       <c r="M113" s="1" t="inlineStr"/>
       <c r="N113" s="1" t="inlineStr">
         <is>
-          <t>L1049: isolated marker/symbol line :: .</t>
+          <t>L994: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O113" s="1" t="inlineStr"/>
@@ -5605,7 +5409,7 @@
       <c r="M114" s="1" t="inlineStr"/>
       <c r="N114" s="1" t="inlineStr">
         <is>
-          <t>L1077: isolated marker/symbol line :: ~</t>
+          <t>L995: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O114" s="1" t="inlineStr"/>
@@ -5636,7 +5440,7 @@
       <c r="M115" s="1" t="inlineStr"/>
       <c r="N115" s="1" t="inlineStr">
         <is>
-          <t>L1078: isolated marker/symbol line :: 0</t>
+          <t>L1002: isolated marker/symbol line :: o</t>
         </is>
       </c>
       <c r="O115" s="1" t="inlineStr"/>
@@ -5667,7 +5471,7 @@
       <c r="M116" s="1" t="inlineStr"/>
       <c r="N116" s="1" t="inlineStr">
         <is>
-          <t>L1079: isolated marker/symbol line :: A</t>
+          <t>L1006: isolated marker/symbol line :: p</t>
         </is>
       </c>
       <c r="O116" s="1" t="inlineStr"/>
@@ -5698,7 +5502,7 @@
       <c r="M117" s="1" t="inlineStr"/>
       <c r="N117" s="1" t="inlineStr">
         <is>
-          <t>L1080: isolated marker/symbol line :: 8</t>
+          <t>L1016: isolated marker/symbol line :: p</t>
         </is>
       </c>
       <c r="O117" s="1" t="inlineStr"/>
@@ -5729,7 +5533,7 @@
       <c r="M118" s="1" t="inlineStr"/>
       <c r="N118" s="1" t="inlineStr">
         <is>
-          <t>L1081: isolated marker/symbol line :: S</t>
+          <t>L1045: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O118" s="1" t="inlineStr"/>
@@ -5760,7 +5564,7 @@
       <c r="M119" s="1" t="inlineStr"/>
       <c r="N119" s="1" t="inlineStr">
         <is>
-          <t>L1094: isolated marker/symbol line :: 0</t>
+          <t>L1047: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O119" s="1" t="inlineStr"/>
@@ -5791,7 +5595,7 @@
       <c r="M120" s="1" t="inlineStr"/>
       <c r="N120" s="1" t="inlineStr">
         <is>
-          <t>L1124: isolated marker/symbol line :: 0</t>
+          <t>L1049: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O120" s="1" t="inlineStr"/>
@@ -5822,7 +5626,7 @@
       <c r="M121" s="1" t="inlineStr"/>
       <c r="N121" s="1" t="inlineStr">
         <is>
-          <t>L1175: isolated marker/symbol line :: r</t>
+          <t>L1077: isolated marker/symbol line :: ~</t>
         </is>
       </c>
       <c r="O121" s="1" t="inlineStr"/>
@@ -5853,7 +5657,7 @@
       <c r="M122" s="1" t="inlineStr"/>
       <c r="N122" s="1" t="inlineStr">
         <is>
-          <t>L1177: isolated marker/symbol line :: A</t>
+          <t>L1078: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O122" s="1" t="inlineStr"/>
@@ -5884,7 +5688,7 @@
       <c r="M123" s="1" t="inlineStr"/>
       <c r="N123" s="1" t="inlineStr">
         <is>
-          <t>L1180: isolated marker/symbol line :: B</t>
+          <t>L1079: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O123" s="1" t="inlineStr"/>
@@ -5915,7 +5719,7 @@
       <c r="M124" s="1" t="inlineStr"/>
       <c r="N124" s="1" t="inlineStr">
         <is>
-          <t>L1220: isolated marker/symbol line :: C</t>
+          <t>L1080: isolated marker/symbol line :: 8</t>
         </is>
       </c>
       <c r="O124" s="1" t="inlineStr"/>
@@ -5946,7 +5750,7 @@
       <c r="M125" s="1" t="inlineStr"/>
       <c r="N125" s="1" t="inlineStr">
         <is>
-          <t>L1230: isolated marker/symbol line :: 2</t>
+          <t>L1081: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O125" s="1" t="inlineStr"/>
@@ -5977,7 +5781,7 @@
       <c r="M126" s="1" t="inlineStr"/>
       <c r="N126" s="1" t="inlineStr">
         <is>
-          <t>L1261: isolated marker/symbol line :: X</t>
+          <t>L1094: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O126" s="1" t="inlineStr"/>
@@ -6008,7 +5812,7 @@
       <c r="M127" s="1" t="inlineStr"/>
       <c r="N127" s="1" t="inlineStr">
         <is>
-          <t>L1292: isolated marker/symbol line :: 4</t>
+          <t>L1124: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O127" s="1" t="inlineStr"/>
@@ -6039,7 +5843,7 @@
       <c r="M128" s="1" t="inlineStr"/>
       <c r="N128" s="1" t="inlineStr">
         <is>
-          <t>L1293: isolated marker/symbol line :: v</t>
+          <t>L1175: isolated marker/symbol line :: r</t>
         </is>
       </c>
       <c r="O128" s="1" t="inlineStr"/>
@@ -6070,7 +5874,7 @@
       <c r="M129" s="1" t="inlineStr"/>
       <c r="N129" s="1" t="inlineStr">
         <is>
-          <t>L1294: isolated marker/symbol line :: 103</t>
+          <t>L1177: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O129" s="1" t="inlineStr"/>
@@ -6101,7 +5905,7 @@
       <c r="M130" s="1" t="inlineStr"/>
       <c r="N130" s="1" t="inlineStr">
         <is>
-          <t>L1300: isolated marker/symbol line :: 00</t>
+          <t>L1180: isolated marker/symbol line :: B</t>
         </is>
       </c>
       <c r="O130" s="1" t="inlineStr"/>
@@ -6132,7 +5936,7 @@
       <c r="M131" s="1" t="inlineStr"/>
       <c r="N131" s="1" t="inlineStr">
         <is>
-          <t>L1319: isolated marker/symbol line :: W</t>
+          <t>L1220: isolated marker/symbol line :: C</t>
         </is>
       </c>
       <c r="O131" s="1" t="inlineStr"/>
@@ -6163,7 +5967,7 @@
       <c r="M132" s="1" t="inlineStr"/>
       <c r="N132" s="1" t="inlineStr">
         <is>
-          <t>L1320: isolated marker/symbol line :: .</t>
+          <t>L1228: stray/suspicious non-ASCII glyph(s): U+56FD CJK UNIFIED IDEOGRAPH-56FD | isolated marker/symbol line :: 国</t>
         </is>
       </c>
       <c r="O132" s="1" t="inlineStr"/>
@@ -6194,7 +5998,7 @@
       <c r="M133" s="1" t="inlineStr"/>
       <c r="N133" s="1" t="inlineStr">
         <is>
-          <t>L1345: isolated marker/symbol line :: 4</t>
+          <t>L1230: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O133" s="1" t="inlineStr"/>
@@ -6225,7 +6029,7 @@
       <c r="M134" s="1" t="inlineStr"/>
       <c r="N134" s="1" t="inlineStr">
         <is>
-          <t>L1346: isolated marker/symbol line :: D</t>
+          <t>L1261: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O134" s="1" t="inlineStr"/>
@@ -6256,7 +6060,7 @@
       <c r="M135" s="1" t="inlineStr"/>
       <c r="N135" s="1" t="inlineStr">
         <is>
-          <t>L1349: isolated marker/symbol line :: 4</t>
+          <t>L1292: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O135" s="1" t="inlineStr"/>
@@ -6287,7 +6091,7 @@
       <c r="M136" s="1" t="inlineStr"/>
       <c r="N136" s="1" t="inlineStr">
         <is>
-          <t>L1350: isolated marker/symbol line :: '</t>
+          <t>L1293: isolated marker/symbol line :: v</t>
         </is>
       </c>
       <c r="O136" s="1" t="inlineStr"/>
@@ -6318,7 +6122,7 @@
       <c r="M137" s="1" t="inlineStr"/>
       <c r="N137" s="1" t="inlineStr">
         <is>
-          <t>L1351: isolated marker/symbol line :: O</t>
+          <t>L1294: isolated marker/symbol line :: 103</t>
         </is>
       </c>
       <c r="O137" s="1" t="inlineStr"/>
@@ -6333,6 +6137,254 @@
       <c r="X137" s="1" t="inlineStr"/>
       <c r="Y137" s="1" t="inlineStr"/>
     </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr"/>
+      <c r="B138" s="1" t="inlineStr"/>
+      <c r="C138" s="1" t="inlineStr"/>
+      <c r="D138" s="1" t="inlineStr"/>
+      <c r="E138" s="1" t="inlineStr"/>
+      <c r="F138" s="1" t="inlineStr"/>
+      <c r="G138" s="1" t="inlineStr"/>
+      <c r="H138" s="1" t="inlineStr"/>
+      <c r="I138" s="1" t="inlineStr"/>
+      <c r="J138" s="1" t="inlineStr"/>
+      <c r="K138" s="1" t="inlineStr"/>
+      <c r="L138" s="1" t="inlineStr"/>
+      <c r="M138" s="1" t="inlineStr"/>
+      <c r="N138" s="1" t="inlineStr">
+        <is>
+          <t>L1300: isolated marker/symbol line :: 00</t>
+        </is>
+      </c>
+      <c r="O138" s="1" t="inlineStr"/>
+      <c r="P138" s="1" t="inlineStr"/>
+      <c r="Q138" s="1" t="inlineStr"/>
+      <c r="R138" s="1" t="inlineStr"/>
+      <c r="S138" s="1" t="inlineStr"/>
+      <c r="T138" s="1" t="inlineStr"/>
+      <c r="U138" s="1" t="inlineStr"/>
+      <c r="V138" s="1" t="inlineStr"/>
+      <c r="W138" s="1" t="inlineStr"/>
+      <c r="X138" s="1" t="inlineStr"/>
+      <c r="Y138" s="1" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr"/>
+      <c r="B139" s="1" t="inlineStr"/>
+      <c r="C139" s="1" t="inlineStr"/>
+      <c r="D139" s="1" t="inlineStr"/>
+      <c r="E139" s="1" t="inlineStr"/>
+      <c r="F139" s="1" t="inlineStr"/>
+      <c r="G139" s="1" t="inlineStr"/>
+      <c r="H139" s="1" t="inlineStr"/>
+      <c r="I139" s="1" t="inlineStr"/>
+      <c r="J139" s="1" t="inlineStr"/>
+      <c r="K139" s="1" t="inlineStr"/>
+      <c r="L139" s="1" t="inlineStr"/>
+      <c r="M139" s="1" t="inlineStr"/>
+      <c r="N139" s="1" t="inlineStr">
+        <is>
+          <t>L1319: isolated marker/symbol line :: W</t>
+        </is>
+      </c>
+      <c r="O139" s="1" t="inlineStr"/>
+      <c r="P139" s="1" t="inlineStr"/>
+      <c r="Q139" s="1" t="inlineStr"/>
+      <c r="R139" s="1" t="inlineStr"/>
+      <c r="S139" s="1" t="inlineStr"/>
+      <c r="T139" s="1" t="inlineStr"/>
+      <c r="U139" s="1" t="inlineStr"/>
+      <c r="V139" s="1" t="inlineStr"/>
+      <c r="W139" s="1" t="inlineStr"/>
+      <c r="X139" s="1" t="inlineStr"/>
+      <c r="Y139" s="1" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr"/>
+      <c r="B140" s="1" t="inlineStr"/>
+      <c r="C140" s="1" t="inlineStr"/>
+      <c r="D140" s="1" t="inlineStr"/>
+      <c r="E140" s="1" t="inlineStr"/>
+      <c r="F140" s="1" t="inlineStr"/>
+      <c r="G140" s="1" t="inlineStr"/>
+      <c r="H140" s="1" t="inlineStr"/>
+      <c r="I140" s="1" t="inlineStr"/>
+      <c r="J140" s="1" t="inlineStr"/>
+      <c r="K140" s="1" t="inlineStr"/>
+      <c r="L140" s="1" t="inlineStr"/>
+      <c r="M140" s="1" t="inlineStr"/>
+      <c r="N140" s="1" t="inlineStr">
+        <is>
+          <t>L1320: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O140" s="1" t="inlineStr"/>
+      <c r="P140" s="1" t="inlineStr"/>
+      <c r="Q140" s="1" t="inlineStr"/>
+      <c r="R140" s="1" t="inlineStr"/>
+      <c r="S140" s="1" t="inlineStr"/>
+      <c r="T140" s="1" t="inlineStr"/>
+      <c r="U140" s="1" t="inlineStr"/>
+      <c r="V140" s="1" t="inlineStr"/>
+      <c r="W140" s="1" t="inlineStr"/>
+      <c r="X140" s="1" t="inlineStr"/>
+      <c r="Y140" s="1" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr"/>
+      <c r="B141" s="1" t="inlineStr"/>
+      <c r="C141" s="1" t="inlineStr"/>
+      <c r="D141" s="1" t="inlineStr"/>
+      <c r="E141" s="1" t="inlineStr"/>
+      <c r="F141" s="1" t="inlineStr"/>
+      <c r="G141" s="1" t="inlineStr"/>
+      <c r="H141" s="1" t="inlineStr"/>
+      <c r="I141" s="1" t="inlineStr"/>
+      <c r="J141" s="1" t="inlineStr"/>
+      <c r="K141" s="1" t="inlineStr"/>
+      <c r="L141" s="1" t="inlineStr"/>
+      <c r="M141" s="1" t="inlineStr"/>
+      <c r="N141" s="1" t="inlineStr">
+        <is>
+          <t>L1345: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O141" s="1" t="inlineStr"/>
+      <c r="P141" s="1" t="inlineStr"/>
+      <c r="Q141" s="1" t="inlineStr"/>
+      <c r="R141" s="1" t="inlineStr"/>
+      <c r="S141" s="1" t="inlineStr"/>
+      <c r="T141" s="1" t="inlineStr"/>
+      <c r="U141" s="1" t="inlineStr"/>
+      <c r="V141" s="1" t="inlineStr"/>
+      <c r="W141" s="1" t="inlineStr"/>
+      <c r="X141" s="1" t="inlineStr"/>
+      <c r="Y141" s="1" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr"/>
+      <c r="B142" s="1" t="inlineStr"/>
+      <c r="C142" s="1" t="inlineStr"/>
+      <c r="D142" s="1" t="inlineStr"/>
+      <c r="E142" s="1" t="inlineStr"/>
+      <c r="F142" s="1" t="inlineStr"/>
+      <c r="G142" s="1" t="inlineStr"/>
+      <c r="H142" s="1" t="inlineStr"/>
+      <c r="I142" s="1" t="inlineStr"/>
+      <c r="J142" s="1" t="inlineStr"/>
+      <c r="K142" s="1" t="inlineStr"/>
+      <c r="L142" s="1" t="inlineStr"/>
+      <c r="M142" s="1" t="inlineStr"/>
+      <c r="N142" s="1" t="inlineStr">
+        <is>
+          <t>L1346: isolated marker/symbol line :: D</t>
+        </is>
+      </c>
+      <c r="O142" s="1" t="inlineStr"/>
+      <c r="P142" s="1" t="inlineStr"/>
+      <c r="Q142" s="1" t="inlineStr"/>
+      <c r="R142" s="1" t="inlineStr"/>
+      <c r="S142" s="1" t="inlineStr"/>
+      <c r="T142" s="1" t="inlineStr"/>
+      <c r="U142" s="1" t="inlineStr"/>
+      <c r="V142" s="1" t="inlineStr"/>
+      <c r="W142" s="1" t="inlineStr"/>
+      <c r="X142" s="1" t="inlineStr"/>
+      <c r="Y142" s="1" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr"/>
+      <c r="B143" s="1" t="inlineStr"/>
+      <c r="C143" s="1" t="inlineStr"/>
+      <c r="D143" s="1" t="inlineStr"/>
+      <c r="E143" s="1" t="inlineStr"/>
+      <c r="F143" s="1" t="inlineStr"/>
+      <c r="G143" s="1" t="inlineStr"/>
+      <c r="H143" s="1" t="inlineStr"/>
+      <c r="I143" s="1" t="inlineStr"/>
+      <c r="J143" s="1" t="inlineStr"/>
+      <c r="K143" s="1" t="inlineStr"/>
+      <c r="L143" s="1" t="inlineStr"/>
+      <c r="M143" s="1" t="inlineStr"/>
+      <c r="N143" s="1" t="inlineStr">
+        <is>
+          <t>L1349: isolated marker/symbol line :: 4</t>
+        </is>
+      </c>
+      <c r="O143" s="1" t="inlineStr"/>
+      <c r="P143" s="1" t="inlineStr"/>
+      <c r="Q143" s="1" t="inlineStr"/>
+      <c r="R143" s="1" t="inlineStr"/>
+      <c r="S143" s="1" t="inlineStr"/>
+      <c r="T143" s="1" t="inlineStr"/>
+      <c r="U143" s="1" t="inlineStr"/>
+      <c r="V143" s="1" t="inlineStr"/>
+      <c r="W143" s="1" t="inlineStr"/>
+      <c r="X143" s="1" t="inlineStr"/>
+      <c r="Y143" s="1" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr"/>
+      <c r="B144" s="1" t="inlineStr"/>
+      <c r="C144" s="1" t="inlineStr"/>
+      <c r="D144" s="1" t="inlineStr"/>
+      <c r="E144" s="1" t="inlineStr"/>
+      <c r="F144" s="1" t="inlineStr"/>
+      <c r="G144" s="1" t="inlineStr"/>
+      <c r="H144" s="1" t="inlineStr"/>
+      <c r="I144" s="1" t="inlineStr"/>
+      <c r="J144" s="1" t="inlineStr"/>
+      <c r="K144" s="1" t="inlineStr"/>
+      <c r="L144" s="1" t="inlineStr"/>
+      <c r="M144" s="1" t="inlineStr"/>
+      <c r="N144" s="1" t="inlineStr">
+        <is>
+          <t>L1350: isolated marker/symbol line :: '</t>
+        </is>
+      </c>
+      <c r="O144" s="1" t="inlineStr"/>
+      <c r="P144" s="1" t="inlineStr"/>
+      <c r="Q144" s="1" t="inlineStr"/>
+      <c r="R144" s="1" t="inlineStr"/>
+      <c r="S144" s="1" t="inlineStr"/>
+      <c r="T144" s="1" t="inlineStr"/>
+      <c r="U144" s="1" t="inlineStr"/>
+      <c r="V144" s="1" t="inlineStr"/>
+      <c r="W144" s="1" t="inlineStr"/>
+      <c r="X144" s="1" t="inlineStr"/>
+      <c r="Y144" s="1" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr"/>
+      <c r="B145" s="1" t="inlineStr"/>
+      <c r="C145" s="1" t="inlineStr"/>
+      <c r="D145" s="1" t="inlineStr"/>
+      <c r="E145" s="1" t="inlineStr"/>
+      <c r="F145" s="1" t="inlineStr"/>
+      <c r="G145" s="1" t="inlineStr"/>
+      <c r="H145" s="1" t="inlineStr"/>
+      <c r="I145" s="1" t="inlineStr"/>
+      <c r="J145" s="1" t="inlineStr"/>
+      <c r="K145" s="1" t="inlineStr"/>
+      <c r="L145" s="1" t="inlineStr"/>
+      <c r="M145" s="1" t="inlineStr"/>
+      <c r="N145" s="1" t="inlineStr">
+        <is>
+          <t>L1351: isolated marker/symbol line :: O</t>
+        </is>
+      </c>
+      <c r="O145" s="1" t="inlineStr"/>
+      <c r="P145" s="1" t="inlineStr"/>
+      <c r="Q145" s="1" t="inlineStr"/>
+      <c r="R145" s="1" t="inlineStr"/>
+      <c r="S145" s="1" t="inlineStr"/>
+      <c r="T145" s="1" t="inlineStr"/>
+      <c r="U145" s="1" t="inlineStr"/>
+      <c r="V145" s="1" t="inlineStr"/>
+      <c r="W145" s="1" t="inlineStr"/>
+      <c r="X145" s="1" t="inlineStr"/>
+      <c r="Y145" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
